--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104515_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104515_W7.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.007</v>
+        <v>4.7568</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0028</v>
+        <v>4.5363</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0043</v>
+        <v>0.2205</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2065</v>
+        <v>1.1744</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7126</v>
+        <v>-0.7286</v>
       </c>
       <c r="I2" t="n">
-        <v>1.919</v>
+        <v>1.903</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4949</v>
+        <v>2.4384</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4608</v>
+        <v>1.4264</v>
       </c>
       <c r="L2" t="n">
-        <v>1.034</v>
+        <v>1.012</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2884</v>
+        <v>-1.264</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.1734</v>
+        <v>-2.1551</v>
       </c>
       <c r="O2" t="n">
-        <v>0.885</v>
+        <v>0.8911</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7059</v>
+        <v>0.4945</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5474</v>
+        <v>0.1482</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1585</v>
+        <v>0.3463</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>E. VILA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0646</v>
+        <v>0.8671</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7749</v>
+        <v>2.5938</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2897</v>
+        <v>-1.7266</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6595</v>
+        <v>0.9358</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.0908</v>
+        <v>0.1551</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4313</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8399</v>
+        <v>2.1829</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6101</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4499</v>
+        <v>1.2661</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4993</v>
+        <v>-1.2471</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4807</v>
+        <v>-0.7617</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0186</v>
+        <v>-0.4854</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9113</v>
+        <v>0.1103</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9084</v>
+        <v>0.4109</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0029</v>
+        <v>-0.3006</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0285</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. VILA</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6808</v>
+        <v>0.7453</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5839</v>
+        <v>0.9174</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9031</v>
+        <v>-0.1721</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9342</v>
+        <v>-0.6683</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1559</v>
+        <v>-2.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7784</v>
+        <v>1.4253</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1968</v>
+        <v>0.8089</v>
       </c>
       <c r="K4" t="n">
-        <v>0.928</v>
+        <v>-0.628</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2688</v>
+        <v>1.4369</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2626</v>
+        <v>-1.4772</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7721</v>
+        <v>-1.4656</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4904</v>
+        <v>-0.0116</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.068</v>
+        <v>1.591</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3871</v>
+        <v>1.0889</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4552</v>
+        <v>0.5021</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0927</v>
+        <v>-0.8603</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4044</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.311</v>
+        <v>-0.6911</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7153</v>
+        <v>1.3832</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.2424</v>
+        <v>-3.2387</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.847</v>
+        <v>-4.8398</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6046</v>
+        <v>1.6012</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4477</v>
+        <v>-1.4748</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.9723</v>
+        <v>-2.9862</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5246</v>
+        <v>1.5114</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7947</v>
+        <v>-1.7638</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8747</v>
+        <v>-1.8536</v>
       </c>
       <c r="O5" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0097</v>
+        <v>0.2949</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.234</v>
+        <v>-0.5742</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2436</v>
+        <v>0.8691</v>
       </c>
       <c r="V5" t="n">
-        <v>2.9566</v>
+        <v>2.9529</v>
       </c>
       <c r="W5" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0554</v>
+        <v>-0.2713</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0917</v>
+        <v>-0.197</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.147</v>
+        <v>-0.0742</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6748</v>
+        <v>-1.6707</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3016</v>
+        <v>-1.2984</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9404</v>
+        <v>-0.9328</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3926</v>
+        <v>0.1718</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6654</v>
+        <v>0.3831</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2728</v>
+        <v>-0.2113</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. LABEYRIE</t>
+          <t>M. SALVO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2194</v>
+        <v>-0.295</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1053</v>
+        <v>0.8268</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3247</v>
+        <v>-1.1218</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5413</v>
+        <v>-1.2984</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3565</v>
+        <v>-0.2185</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8979</v>
+        <v>-1.0799</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4965</v>
+        <v>0.3647</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1083</v>
+        <v>0.3275</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3883</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9552</v>
+        <v>-1.6631</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4648</v>
+        <v>-0.546</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4904</v>
+        <v>-1.1171</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4246</v>
+        <v>0.0929</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0302</v>
+        <v>0.4621</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4549</v>
+        <v>-0.3692</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,49 +1033,49 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3161</v>
+        <v>-0.3159</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7539</v>
+        <v>-0.7567</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4378</v>
+        <v>0.4408</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0014</v>
+        <v>0.0028</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1559</v>
+        <v>-0.1551</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1087,10 +1087,10 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SALVO</t>
+          <t>L. LABEYRIE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7909</v>
+        <v>-0.8012</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4026</v>
+        <v>1.6185</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1935</v>
+        <v>-2.4197</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3045</v>
+        <v>1.5498</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2223</v>
+        <v>-0.348</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0822</v>
+        <v>1.8978</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3663</v>
+        <v>3.4863</v>
       </c>
       <c r="K9" t="n">
-        <v>0.329</v>
+        <v>1.1032</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>2.3832</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6708</v>
+        <v>-1.9365</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5513</v>
+        <v>-1.4511</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1195</v>
+        <v>-0.4854</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3938</v>
+        <v>-0.1721</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0363</v>
+        <v>-0.5021</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4301</v>
+        <v>0.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0005</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3143</v>
+        <v>-0.2293</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6862</v>
+        <v>-0.5747</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4835</v>
+        <v>-0.5018</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5292</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0263</v>
+        <v>-1.031</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0618</v>
+        <v>1.0322</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4404</v>
+        <v>1.4199</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5453</v>
+        <v>-1.534</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8976</v>
+        <v>-0.8907</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7098</v>
+        <v>0.9255</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8922</v>
+        <v>1.0148</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1824</v>
+        <v>-0.0893</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2488</v>
+        <v>-4.5752</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9879</v>
+        <v>-3.3423</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2609</v>
+        <v>-1.2329</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.8729</v>
+        <v>-4.8676</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.0577</v>
+        <v>-3.0533</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8152</v>
+        <v>-1.8143</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.8749</v>
+        <v>-2.889</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4515</v>
+        <v>-1.4586</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.998</v>
+        <v>-1.9786</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6062</v>
+        <v>-1.5946</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1905</v>
+        <v>0.4713</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8861</v>
+        <v>-0.2257</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6956</v>
+        <v>0.697</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0167</v>
+        <v>-5.665</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.215</v>
+        <v>-4.0735</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8017</v>
+        <v>-1.5915</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.9263</v>
+        <v>-3.9343</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9942</v>
+        <v>-0.9965000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.9321</v>
+        <v>-2.9378</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0406</v>
+        <v>-1.0674</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1243</v>
+        <v>0.1099</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1649</v>
+        <v>-1.1773</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8857</v>
+        <v>-2.8668</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1185</v>
+        <v>-1.1064</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7672</v>
+        <v>-1.7604</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0587</v>
+        <v>0.4365</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3357</v>
+        <v>0.5269</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.277</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.7605</v>
+        <v>-6.8856</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.243</v>
+        <v>-4.658</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5175</v>
+        <v>-2.2275</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.8144</v>
+        <v>-5.8017</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.6957</v>
+        <v>-2.6778</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.1187</v>
+        <v>-3.124</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.532</v>
+        <v>-3.5497</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.8842</v>
+        <v>-2.8979</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2824</v>
+        <v>-2.2521</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.0479</v>
+        <v>-2.026</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3997</v>
+        <v>-0.5391</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4426</v>
+        <v>-0.832</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0429</v>
+        <v>0.2929</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.2515</v>
+        <v>-12.5519</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.863899999999999</v>
+        <v>-3.455100000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.387499999999999</v>
+        <v>-9.096499999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-18.2949</v>
+        <v>-18.3187</v>
       </c>
       <c r="H14" t="n">
-        <v>-15.7356</v>
+        <v>-15.7253</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.5592</v>
+        <v>-2.5935</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8438999999999997</v>
+        <v>0.6117999999999992</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.008</v>
+        <v>-1.1415</v>
       </c>
       <c r="L14" t="n">
-        <v>1.851800000000001</v>
+        <v>1.7536</v>
       </c>
       <c r="M14" t="n">
-        <v>-19.1387</v>
+        <v>-18.9304</v>
       </c>
       <c r="N14" t="n">
-        <v>-14.7276</v>
+        <v>-14.5836</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.411</v>
+        <v>-4.3468</v>
       </c>
       <c r="P14" t="n">
-        <v>2.268300000000001</v>
+        <v>2.2763</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.4758</v>
+        <v>-12.5198</v>
       </c>
       <c r="R14" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1606</v>
+        <v>3.8775</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1796</v>
+        <v>1.9009</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9809</v>
+        <v>1.9766</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3855999999999995</v>
+        <v>-0.387</v>
       </c>
       <c r="W14" t="n">
-        <v>6.5884</v>
+        <v>6.5518</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.974</v>
+        <v>-6.9386</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1559</v>
+        <v>5.1042</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9414</v>
+        <v>3.5831</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2145</v>
+        <v>1.5211</v>
       </c>
       <c r="G15" t="n">
-        <v>4.5777</v>
+        <v>4.2901</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4963</v>
+        <v>3.5992</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0814</v>
+        <v>0.6909</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1421</v>
+        <v>5.3199</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8285</v>
+        <v>4.1886</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3136</v>
+        <v>1.1313</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4356</v>
+        <v>-1.0298</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3321</v>
+        <v>-0.5893</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7678</v>
+        <v>-0.4405</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.6805</v>
+        <v>-2.5039</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>2.2763</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4479</v>
+        <v>0.3393</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3871</v>
+        <v>-0.0931</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0608</v>
+        <v>0.4324</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.0965</v>
+        <v>0.7025</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>0.8603</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1892</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9514</v>
+        <v>4.9441</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3996</v>
+        <v>4.563</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5518</v>
+        <v>0.3811</v>
       </c>
       <c r="G16" t="n">
-        <v>4.3073</v>
+        <v>4.5831</v>
       </c>
       <c r="H16" t="n">
-        <v>3.609</v>
+        <v>1.4964</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6983</v>
+        <v>3.0867</v>
       </c>
       <c r="J16" t="n">
-        <v>5.3567</v>
+        <v>4.1218</v>
       </c>
       <c r="K16" t="n">
-        <v>4.208</v>
+        <v>1.8131</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1487</v>
+        <v>2.3087</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0494</v>
+        <v>0.4613</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.599</v>
+        <v>-0.3168</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4504</v>
+        <v>0.778</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.4952</v>
+        <v>-0.6829</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2683</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1639</v>
+        <v>0.2197</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3297</v>
+        <v>0.0346</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4936</v>
+        <v>0.1851</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7071</v>
+        <v>-0.0863</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8678</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-1.1758</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>A. TOMIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.9757</v>
+        <v>4.2287</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6944</v>
+        <v>2.6142</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2812</v>
+        <v>1.6145</v>
       </c>
       <c r="G17" t="n">
-        <v>3.142</v>
+        <v>3.1184</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1054</v>
+        <v>3.5769</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0365</v>
+        <v>-0.4584</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2345</v>
+        <v>4.0035</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9657</v>
+        <v>3.3332</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2688</v>
+        <v>0.6703</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9074</v>
+        <v>-0.8851</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1397</v>
+        <v>0.2437</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7678</v>
+        <v>-1.1287</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-2.7316</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0587</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0212</v>
+        <v>0.095</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0799</v>
+        <v>0.4509</v>
       </c>
       <c r="V17" t="n">
-        <v>1.7997</v>
+        <v>1.2472</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7997</v>
+        <v>1.2472</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.8787</v>
+        <v>3.6021</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6528</v>
+        <v>1.163</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2258</v>
+        <v>2.4391</v>
       </c>
       <c r="G18" t="n">
-        <v>4.1572</v>
+        <v>4.1674</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9133</v>
+        <v>0.9215</v>
       </c>
       <c r="I18" t="n">
-        <v>3.244</v>
+        <v>3.246</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8717</v>
+        <v>2.8588</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0764</v>
+        <v>-0.0829</v>
       </c>
       <c r="L18" t="n">
-        <v>2.948</v>
+        <v>2.9417</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2856</v>
+        <v>1.3087</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9896</v>
+        <v>1.0044</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6288</v>
+        <v>0.3452</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5958</v>
+        <v>0.1253</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0329</v>
+        <v>0.22</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. TOMIC</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.5801</v>
+        <v>3.4589</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3056</v>
+        <v>2.1819</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2745</v>
+        <v>1.277</v>
       </c>
       <c r="G19" t="n">
-        <v>3.1312</v>
+        <v>3.1417</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5976</v>
+        <v>1.0976</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4664</v>
+        <v>2.0441</v>
       </c>
       <c r="J19" t="n">
-        <v>4.0343</v>
+        <v>2.2066</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3626</v>
+        <v>0.9405</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6717</v>
+        <v>1.2661</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.903</v>
+        <v>0.9351</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2351</v>
+        <v>0.157</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1381</v>
+        <v>0.778</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.722</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.124</v>
+        <v>-0.5642</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2601</v>
+        <v>-0.4509</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1361</v>
+        <v>-0.1133</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2534</v>
+        <v>1.792</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2534</v>
+        <v>1.792</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8058</v>
+        <v>0.9328</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4511</v>
+        <v>-0.3399</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2569</v>
+        <v>1.2727</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8437</v>
+        <v>0.8525</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6939</v>
+        <v>1.6999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.8475</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0337</v>
+        <v>-0.0402</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6407</v>
+        <v>0.6378</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8773</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>1.0532</v>
+        <v>1.0622</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2646</v>
+        <v>-0.1473</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4174</v>
+        <v>-0.2998</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1527</v>
+        <v>0.1524</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.424</v>
+        <v>0.7033</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8752</v>
+        <v>0.9862</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4512</v>
+        <v>-0.2829</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7317</v>
+        <v>-0.7296</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1559</v>
+        <v>0.1551</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.8847</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9232</v>
+        <v>0.9191</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6549</v>
+        <v>-1.6487</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6927</v>
+        <v>-0.6895</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.366</v>
+        <v>-0.0907</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1573</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.404</v>
+        <v>-0.1362</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1813</v>
+        <v>0.2937</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5853</v>
+        <v>-0.4299</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3384</v>
+        <v>1.3505</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6853</v>
+        <v>0.6918</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6531</v>
+        <v>0.6587</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1219</v>
+        <v>1.1184</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4502</v>
+        <v>0.4482</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2165</v>
+        <v>0.232</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3717</v>
+        <v>-0.1288</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4869</v>
+        <v>-0.3695</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1152</v>
+        <v>0.2407</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6511</v>
+        <v>-1.4244</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9319</v>
+        <v>-1.4912</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7192</v>
+        <v>0.0668</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7823</v>
+        <v>-0.7778</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3665</v>
+        <v>0.3676</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1488</v>
+        <v>-1.1454</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0557</v>
+        <v>-0.0799</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2109</v>
+        <v>0.1961</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7266</v>
+        <v>-0.6979</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1556</v>
+        <v>0.1715</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8007</v>
+        <v>-0.5783</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8347</v>
+        <v>-0.3627</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.966</v>
+        <v>-0.2157</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.007</v>
+        <v>-2.4831</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1263</v>
+        <v>-2.0413</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8807</v>
+        <v>-0.4418</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.452</v>
+        <v>-0.4461</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2193</v>
+        <v>1.2206</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6712</v>
+        <v>-1.6667</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5034999999999999</v>
+        <v>-0.5218</v>
       </c>
       <c r="K24" t="n">
-        <v>1.0319</v>
+        <v>1.0202</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0515</v>
+        <v>0.0757</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-0.4436</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6079</v>
+        <v>-0.4904</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3593</v>
+        <v>0.0468</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4581</v>
+        <v>-3.3127</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.1535</v>
+        <v>-2.416</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3046</v>
+        <v>-0.8966</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.2367</v>
+        <v>-1.2315</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8931</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.1298</v>
+        <v>-2.1302</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9528</v>
+        <v>-0.9757</v>
       </c>
       <c r="K25" t="n">
-        <v>1.257</v>
+        <v>1.2443</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.2098</v>
+        <v>-2.22</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2839</v>
+        <v>-0.2558</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.3639</v>
+        <v>-0.3457</v>
       </c>
       <c r="O25" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4482</v>
+        <v>-0.3088</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1603</v>
+        <v>-0.0746</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6085</v>
+        <v>-0.2342</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>13.2514</v>
+        <v>15.6177</v>
       </c>
       <c r="E26" t="n">
-        <v>9.387499999999996</v>
+        <v>9.096700000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>3.8637</v>
+        <v>6.521099999999998</v>
       </c>
       <c r="G26" t="n">
-        <v>18.2948</v>
+        <v>18.3187</v>
       </c>
       <c r="H26" t="n">
-        <v>15.7356</v>
+        <v>15.7253</v>
       </c>
       <c r="I26" t="n">
-        <v>2.559200000000001</v>
+        <v>2.593499999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>19.1387</v>
+        <v>18.93050000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>14.7276</v>
+        <v>14.5837</v>
       </c>
       <c r="L26" t="n">
-        <v>4.4109</v>
+        <v>4.347</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.8439000000000003</v>
+        <v>-0.6119</v>
       </c>
       <c r="N26" t="n">
-        <v>1.008</v>
+        <v>1.1415</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.8518</v>
+        <v>-1.7534</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q26" t="n">
-        <v>-14.7442</v>
+        <v>-14.7961</v>
       </c>
       <c r="R26" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.1605</v>
+        <v>-0.8116000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.981</v>
+        <v>-1.9768</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.1797</v>
+        <v>1.1651</v>
       </c>
       <c r="V26" t="n">
-        <v>0.3855999999999997</v>
+        <v>0.387</v>
       </c>
       <c r="W26" t="n">
-        <v>6.974000000000001</v>
+        <v>6.9387</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.5884</v>
+        <v>-6.5518</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104515_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104515_W7.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.9386</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.1758</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104515_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-6.5518</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
